--- a/artfynd/A 57978-2025 artfynd.xlsx
+++ b/artfynd/A 57978-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121430483</v>
+        <v>54480040</v>
       </c>
       <c r="B2" t="n">
-        <v>98147</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,38 +686,45 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219874</v>
+        <v>219811</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stora Kumlan, Vstm</t>
+          <t>Klosstjärn, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491794</v>
+        <v>491789</v>
       </c>
       <c r="R2" t="n">
-        <v>6648461</v>
+        <v>6648542</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,12 +751,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2015-07-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2015-07-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,15 +771,640 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Thyra Lundell</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Thyra Lundell</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>54480052</v>
+      </c>
+      <c r="B3" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Klosstjärn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>491789</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6648542</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2015-07-17</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2015-07-17</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Thyra Lundell</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Thyra Lundell</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>16543517</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99153</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Klosstjärn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>491786</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6648595</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2014-07-02</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2014-07-02</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Thyra Lundell</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Thyra Lundell</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>16849313</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99153</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Klosstjärn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>491789</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6648595</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2014-07-02</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2014-07-02</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Thyra Lundell</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Thyra Lundell</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121430483</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99153</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Stora Kumlan, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>491794</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6648461</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-06-18</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-06-18</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Anna-Lotta Hellqvist</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Anna-Lotta Hellqvist, Lisa Stridh, Emma Karlsson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121430484</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99153</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Stora Kumlan, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>491782</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6648536</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-06-18</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-06-18</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anna-Lotta Hellqvist</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anna-Lotta Hellqvist, Lisa Stridh, Emma Karlsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>54365656</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99156</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219875</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Platanthera chlorantha</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Klosstjärn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>491789</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6648595</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2015-07-11</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2015-07-11</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Thyra Lundell</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Thyra Lundell</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57978-2025 artfynd.xlsx
+++ b/artfynd/A 57978-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54480040</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54480052</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -995,6 +1010,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16543517</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1099,6 +1119,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16849313</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1200,6 +1225,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121430483</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1297,6 +1327,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121430484</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1405,8 +1440,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54365656</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>